--- a/y_test.xlsx
+++ b/y_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,74 +437,82 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>978</v>
+        <v>6.75343791859778</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1082</v>
+        <v>6.88653164253051</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>297</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>706</v>
+        <v>6.987490247000991</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>301</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>724</v>
+        <v>6.561030665896573</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>305</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>586</v>
+        <v>6.586171654854675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>309</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>586</v>
+        <v>6.375024819828097</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>310</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>484</v>
+        <v>6.375024819828097</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>315</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>466</v>
+        <v>6.184148890937483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>319</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>436</v>
+        <v>6.146329257668897</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>6.07993319509559</v>
       </c>
     </row>
   </sheetData>
